--- a/cookie_order_forms/017_halloween_candy_gram_order_form--cookie_order_forms.xlsx
+++ b/cookie_order_forms/017_halloween_candy_gram_order_form--cookie_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>field_9</t>
+          <t>candy_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Field 9</t>
+          <t>Candy 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>field_10</t>
+          <t>candy_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Field 10</t>
+          <t>Candy 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -814,322 +814,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>candy1</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Candy 1</t>
+          <t>Payment Type</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>candy2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Candy 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>candy3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Candy 3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>candy4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Candy 4</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>candy5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Candy 5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>candy6</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Candy 6</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>candy7</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Candy 7</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>candy8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Candy 8</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>total_items</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Total Items</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Special Instructions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>payment_type</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Payment Type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>special_instructions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Special Instructions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1144,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C199"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1568,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mn</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1422,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1456,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nd</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1490,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1507,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1524,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1541,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>pr</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1558,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pr</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1575,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ri</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1592,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1609,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1626,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1643,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1660,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1677,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>vt</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1694,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -2010,12 +1711,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -2027,12 +1728,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -2044,12 +1745,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -2061,12 +1762,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2078,12 +1779,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>qc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>QC</t>
         </is>
       </c>
     </row>
@@ -2095,12 +1796,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>mb</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>MB</t>
         </is>
       </c>
     </row>
@@ -2112,12 +1813,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mb</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
@@ -2129,12 +1830,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -2146,12 +1847,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>sk</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SK</t>
         </is>
       </c>
     </row>
@@ -2163,12 +1864,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sk</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>NL</t>
         </is>
       </c>
     </row>
@@ -2180,12 +1881,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>pe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
@@ -2197,12 +1898,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pe</t>
+          <t>nt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>NT</t>
         </is>
       </c>
     </row>
@@ -2214,12 +1915,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>yk</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>YK</t>
         </is>
       </c>
     </row>
@@ -2231,12 +1932,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>yk</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YK</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -2248,284 +1949,284 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>nb</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>NB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nb</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>mb</t>
+          <t>as</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>sk</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>yk</t>
+          <t>de</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>YK</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>pe</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>field_8_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2238,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>al</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2255,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ak</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2272,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2289,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>az</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2306,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2323,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2340,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2357,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ct</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -2673,12 +2374,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2391,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fl</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2408,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ga</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2425,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2442,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2459,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2476,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2493,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2510,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2527,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ky</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2544,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>la</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2561,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2578,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2595,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -2911,12 +2612,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2629,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>mn</t>
+          <t>pr</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -2945,12 +2646,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2663,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -2979,12 +2680,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2697,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -3013,12 +2714,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -3030,12 +2731,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -3047,12 +2748,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -3064,12 +2765,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -3081,12 +2782,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -3098,12 +2799,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -3115,12 +2816,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nd</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -3132,12 +2833,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -3149,12 +2850,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3166,12 +2867,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>qc</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>QC</t>
         </is>
       </c>
     </row>
@@ -3183,12 +2884,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>mb</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MB</t>
         </is>
       </c>
     </row>
@@ -3200,12 +2901,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>pr</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
@@ -3217,12 +2918,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ri</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -3234,12 +2935,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>sk</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SK</t>
         </is>
       </c>
     </row>
@@ -3251,12 +2952,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NL</t>
         </is>
       </c>
     </row>
@@ -3268,12 +2969,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>pe</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>PE</t>
         </is>
       </c>
     </row>
@@ -3285,12 +2986,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>nt</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NT</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3003,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>yk</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>YK</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3020,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>vt</t>
+          <t>ns</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -3336,1200 +3037,163 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>nb</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NB</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_1_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_1_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_1_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_2_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_2_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>candy_2_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>qc</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>QC</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>mb</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>cash</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>credit</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>field_8_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>sk</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>nl</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>pe</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>nt</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>yk</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>YK</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>nb</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>NB</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>mb</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>field_8_choices</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>qc</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>candy1</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>candy1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>candy2</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>candy2</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>candy3</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>candy3</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>candy4</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>candy4</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>candy5</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>candy5</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>candy6</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>candy6</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>candy7</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>candy7</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>field_9_choices</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>candy8</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>candy8</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>candy1</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>candy1</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>candy2</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>candy2</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>candy3</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>candy3</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>candy4</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>candy4</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>candy5</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>candy5</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>candy6</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>candy6</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>candy7</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>candy7</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>field_10_choices</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>candy8</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>candy8</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>candy1_choices</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>candy1_choices</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>candy1_choices</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>candy1_choices</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>candy2_choices</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>candy2_choices</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>candy2_choices</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>candy2_choices</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>candy3_choices</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>candy3_choices</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>candy3_choices</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>candy3_choices</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>candy4_choices</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>candy4_choices</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>candy4_choices</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>candy4_choices</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>candy5_choices</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>candy5_choices</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>candy5_choices</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>candy5_choices</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>candy6_choices</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>candy6_choices</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>candy6_choices</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>candy6_choices</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>candy7_choices</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>candy7_choices</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>candy7_choices</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>candy7_choices</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>candy8_choices</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>item1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>candy8_choices</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>item2</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>candy8_choices</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>item3</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>candy8_choices</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>item4</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>payment_type_choices</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>payment_type_choices</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>credit</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>credit</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>payment_type_choices</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
